--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484368_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484368_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9656</v>
+        <v>7.7828</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1736</v>
+        <v>6.0725</v>
       </c>
       <c r="F2" t="n">
-        <v>1.792</v>
+        <v>1.7103</v>
       </c>
       <c r="G2" t="n">
         <v>4.5041</v>
@@ -610,13 +610,13 @@
         <v>2.9301</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2895</v>
+        <v>0.1066</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.22</v>
+        <v>-0.3211</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5094</v>
+        <v>0.4277</v>
       </c>
       <c r="V2" t="n">
         <v>1.2186</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.134</v>
+        <v>6.2874</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8102</v>
+        <v>3.8818</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3239</v>
+        <v>2.4056</v>
       </c>
       <c r="G3" t="n">
         <v>6.0838</v>
@@ -688,13 +688,13 @@
         <v>1.1721</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1684</v>
+        <v>0.985</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5915</v>
+        <v>0.4802</v>
       </c>
       <c r="U3" t="n">
-        <v>0.423</v>
+        <v>0.5047</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7418</v>
+        <v>5.3001</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9121</v>
+        <v>4.5793</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8297</v>
+        <v>0.7208</v>
       </c>
       <c r="G4" t="n">
         <v>5.4558</v>
@@ -766,13 +766,13 @@
         <v>1.3674</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3698</v>
+        <v>0.1885</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6657</v>
+        <v>0.0015</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2959</v>
+        <v>0.187</v>
       </c>
       <c r="V4" t="n">
         <v>1.2186</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5617</v>
+        <v>2.9767</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4748</v>
+        <v>0.7264</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0869</v>
+        <v>2.2503</v>
       </c>
       <c r="G5" t="n">
         <v>0.3128</v>
@@ -844,13 +844,13 @@
         <v>2.1488</v>
       </c>
       <c r="S5" t="n">
-        <v>2.3541</v>
+        <v>1.7691</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9839</v>
+        <v>1.2355</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3702</v>
+        <v>0.5336</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2772</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>J. NOGUES JARNE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.467</v>
+        <v>2.8951</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07580000000000001</v>
+        <v>2.8642</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3912</v>
+        <v>0.031</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1764</v>
+        <v>3.3639</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.177</v>
+        <v>1.5155</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0005999999999999999</v>
+        <v>1.8484</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5708</v>
+        <v>3.6633</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5718</v>
+        <v>1.6795</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001</v>
+        <v>1.9838</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3944</v>
+        <v>-0.2994</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3948</v>
+        <v>-0.1639</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0004</v>
+        <v>-0.1354</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
         <v>1.9534</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4737</v>
+        <v>0.3824</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5172</v>
+        <v>0.1776</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0434</v>
+        <v>0.2048</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1638</v>
+        <v>-1.8279</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1638</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. NOGUES JARNE</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3872</v>
+        <v>2.8871</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6014</v>
+        <v>0.2781</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2142</v>
+        <v>2.6091</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3639</v>
+        <v>-0.1764</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5155</v>
+        <v>-0.177</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8484</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6633</v>
+        <v>-0.5708</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6795</v>
+        <v>-0.5718</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9838</v>
+        <v>0.001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2994</v>
+        <v>0.3944</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1639</v>
+        <v>0.3948</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1354</v>
+        <v>-0.0004</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>1.9534</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1254</v>
+        <v>-0.0536</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0851</v>
+        <v>-0.3149</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0403</v>
+        <v>0.2613</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.8279</v>
+        <v>1.1638</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.1638</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9694</v>
+        <v>1.6095</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8759</v>
+        <v>0.6365</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0935</v>
+        <v>0.973</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5643</v>
+        <v>0.6093</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6861</v>
+        <v>0.3395</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1218</v>
+        <v>0.2698</v>
       </c>
       <c r="J8" t="n">
-        <v>0.305</v>
+        <v>2.2569</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0217</v>
+        <v>1.3123</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2833</v>
+        <v>0.9445</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2593</v>
+        <v>-1.6476</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6644</v>
+        <v>-0.9729</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4051</v>
+        <v>-0.6747</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9534</v>
+        <v>0.3907</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9534</v>
+        <v>2.3441</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9475</v>
+        <v>0.3323</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0384</v>
+        <v>0.0558</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9859</v>
+        <v>0.2764</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4959</v>
+        <v>0.2772</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1052</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>A. RUIZ CAÑAMERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1663</v>
+        <v>1.2303</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2473</v>
+        <v>0.5726</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9191</v>
+        <v>0.6577</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9301</v>
+        <v>0.5643</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8366</v>
+        <v>0.6861</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7667</v>
+        <v>-0.1218</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1245</v>
+        <v>0.305</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1023</v>
+        <v>0.0217</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2268</v>
+        <v>0.2833</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1944</v>
+        <v>0.2593</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7342</v>
+        <v>0.6644</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5399</v>
+        <v>-0.4051</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8425</v>
+        <v>0.2084</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8173</v>
+        <v>-0.3417</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0253</v>
+        <v>0.5501</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2772</v>
+        <v>-1.4959</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5545</v>
+        <v>0.6093</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2772</v>
+        <v>-2.1052</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9436</v>
+        <v>1.1142</v>
       </c>
       <c r="E10" t="n">
-        <v>1.2927</v>
+        <v>0.0044</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3491</v>
+        <v>1.1097</v>
       </c>
       <c r="G10" t="n">
-        <v>0.126</v>
+        <v>-0.9301</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3796</v>
+        <v>0.8366</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2536</v>
+        <v>-1.7667</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7687</v>
+        <v>-1.1245</v>
       </c>
       <c r="K10" t="n">
-        <v>2.2128</v>
+        <v>0.1023</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4441</v>
+        <v>-1.2268</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6427</v>
+        <v>0.1944</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8332000000000001</v>
+        <v>0.7342</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8095</v>
+        <v>-0.5399</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1488</v>
+        <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>2.2082</v>
+        <v>0.7903</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2355</v>
+        <v>0.5744</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9727</v>
+        <v>0.2159</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2186</v>
+        <v>0.5545</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8279</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.711</v>
+        <v>0.0118</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0713</v>
+        <v>-2.3789</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7823</v>
+        <v>2.3906</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6093</v>
+        <v>-1.3537</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3395</v>
+        <v>0.8307</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2698</v>
+        <v>-2.1844</v>
       </c>
       <c r="J11" t="n">
-        <v>2.2569</v>
+        <v>-1.4086</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3123</v>
+        <v>0.3709</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9445</v>
+        <v>-1.7795</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6476</v>
+        <v>0.0549</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9729</v>
+        <v>0.4597</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6747</v>
+        <v>-0.4049</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3441</v>
+        <v>1.5627</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5662</v>
+        <v>1.1115</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.652</v>
+        <v>0.3385</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0858</v>
+        <v>0.773</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2772</v>
+        <v>-0.3321</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2772</v>
+        <v>-0.3321</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6341</v>
+        <v>-0.1105</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9744</v>
+        <v>0.4838</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6085</v>
+        <v>-0.5943000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.3537</v>
+        <v>0.126</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8307</v>
+        <v>1.3796</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1844</v>
+        <v>-1.2536</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4086</v>
+        <v>1.7687</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3709</v>
+        <v>2.2128</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.7795</v>
+        <v>-0.4441</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0549</v>
+        <v>-1.6427</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4597</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4049</v>
+        <v>-0.8095</v>
       </c>
       <c r="P12" t="n">
-        <v>0.586</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5627</v>
+        <v>2.1488</v>
       </c>
       <c r="S12" t="n">
-        <v>1.7339</v>
+        <v>1.1542</v>
       </c>
       <c r="T12" t="n">
-        <v>0.743</v>
+        <v>0.4266</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9909</v>
+        <v>0.7276</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3321</v>
+        <v>-0.6093</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3321</v>
+        <v>1.2186</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>31.6817</v>
+        <v>31.9845</v>
       </c>
       <c r="E13" t="n">
-        <v>17.4181</v>
+        <v>17.7207</v>
       </c>
       <c r="F13" t="n">
         <v>14.2638</v>
@@ -1435,7 +1435,7 @@
         <v>18.5598</v>
       </c>
       <c r="H13" t="n">
-        <v>8.4384</v>
+        <v>8.438400000000001</v>
       </c>
       <c r="I13" t="n">
         <v>10.1213</v>
@@ -1444,7 +1444,7 @@
         <v>23.1536</v>
       </c>
       <c r="K13" t="n">
-        <v>8.307500000000001</v>
+        <v>8.307499999999999</v>
       </c>
       <c r="L13" t="n">
         <v>14.8461</v>
@@ -1453,10 +1453,10 @@
         <v>-4.5939</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1306000000000003</v>
+        <v>0.1305999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.724699999999999</v>
+        <v>-4.7247</v>
       </c>
       <c r="P13" t="n">
         <v>6.836900000000001</v>
@@ -1468,13 +1468,13 @@
         <v>20.5109</v>
       </c>
       <c r="S13" t="n">
-        <v>6.6722</v>
+        <v>6.974699999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0098</v>
+        <v>2.3124</v>
       </c>
       <c r="U13" t="n">
-        <v>4.6622</v>
+        <v>4.6621</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3870000000000005</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5351</v>
+        <v>0.4054</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1368</v>
+        <v>2.0357</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6017</v>
+        <v>-1.6303</v>
       </c>
       <c r="G14" t="n">
         <v>1.7012</v>
@@ -1546,13 +1546,13 @@
         <v>1.3674</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1194</v>
+        <v>-0.0103</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2337</v>
+        <v>-0.3349</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3531</v>
+        <v>0.3245</v>
       </c>
       <c r="V14" t="n">
         <v>0.2772</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.8773</v>
+        <v>-0.622</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0143</v>
+        <v>0.2165</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8915999999999999</v>
+        <v>-0.8385</v>
       </c>
       <c r="G15" t="n">
         <v>-0.2541</v>
@@ -1624,13 +1624,13 @@
         <v>0.9767</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2911</v>
+        <v>-0.0358</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6052</v>
+        <v>-0.403</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3141</v>
+        <v>0.3672</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3321</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.8374</v>
+        <v>-1.6075</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5763</v>
+        <v>0.1346</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2611</v>
+        <v>-1.7421</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.7349</v>
+        <v>-0.0404</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4434</v>
+        <v>0.473</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.2915</v>
+        <v>-0.5134</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.2033</v>
+        <v>3.6962</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6102</v>
+        <v>1.1064</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5931999999999999</v>
+        <v>2.5898</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.5316</v>
+        <v>-3.7366</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.6334</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.6984</v>
+        <v>-3.1032</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7814</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7581</v>
+        <v>2.3441</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6532</v>
+        <v>-1.223</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8335</v>
+        <v>-0.8734</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1803</v>
+        <v>-0.3496</v>
       </c>
       <c r="V16" t="n">
-        <v>2.7693</v>
+        <v>1.2186</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4373</v>
+        <v>1.2186</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>H. CANTALEJO DELGADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.8642</v>
+        <v>-1.9042</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.013</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7966</v>
+        <v>-1.8912</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0404</v>
+        <v>-1.398</v>
       </c>
       <c r="H17" t="n">
-        <v>0.473</v>
+        <v>0.4502</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5134</v>
+        <v>-1.8482</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6962</v>
+        <v>1.1047</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1064</v>
+        <v>1.0642</v>
       </c>
       <c r="L17" t="n">
-        <v>2.5898</v>
+        <v>0.0405</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.7366</v>
+        <v>-2.5026</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6334</v>
+        <v>-0.614</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.1032</v>
+        <v>-1.8887</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5627</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3441</v>
+        <v>0.586</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4797</v>
+        <v>0.1616</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0756</v>
+        <v>-0.141</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.404</v>
+        <v>0.3026</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2186</v>
+        <v>-0.2772</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H. CANTALEJO DELGADO</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0053</v>
+        <v>-2.1176</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1141</v>
+        <v>-0.4752</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8912</v>
+        <v>-1.6424</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.398</v>
+        <v>-4.7349</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4502</v>
+        <v>-1.4434</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.8482</v>
+        <v>-3.2915</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1047</v>
+        <v>-1.2033</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0642</v>
+        <v>-0.6102</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0405</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5026</v>
+        <v>-3.5316</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.614</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.8887</v>
+        <v>-2.6984</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0605</v>
+        <v>-0.9334</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2421</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3026</v>
+        <v>-0.201</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2772</v>
+        <v>2.7693</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6405</v>
+        <v>-2.6184</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4294</v>
+        <v>-0.7328</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2111</v>
+        <v>-1.8856</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6294999999999999</v>
@@ -1936,13 +1936,13 @@
         <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4919</v>
+        <v>-0.4698</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1899</v>
+        <v>-0.1134</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6818</v>
+        <v>-0.3564</v>
       </c>
       <c r="V19" t="n">
         <v>-2.1052</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9802</v>
+        <v>-2.7987</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6323</v>
+        <v>-1.5312</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3479</v>
+        <v>-1.2676</v>
       </c>
       <c r="G20" t="n">
         <v>-2.3536</v>
@@ -2014,13 +2014,13 @@
         <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4313</v>
+        <v>-1.2498</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9546</v>
+        <v>-0.8535</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4767</v>
+        <v>-0.3963</v>
       </c>
       <c r="V20" t="n">
         <v>0.6093</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.165</v>
+        <v>-3.1493</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6863</v>
+        <v>-0.8885</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4787</v>
+        <v>-2.2608</v>
       </c>
       <c r="G21" t="n">
         <v>-3.494</v>
@@ -2092,13 +2092,13 @@
         <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7296</v>
+        <v>-0.714</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1594</v>
+        <v>-0.3617</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5702</v>
+        <v>-0.3523</v>
       </c>
       <c r="V21" t="n">
         <v>0.2772</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2234</v>
+        <v>-3.1638</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6021</v>
+        <v>-3.7033</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3787</v>
+        <v>0.5394</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9979</v>
@@ -2170,13 +2170,13 @@
         <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0534</v>
+        <v>0.0062</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1294</v>
+        <v>0.0283</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1828</v>
+        <v>-0.0221</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9127</v>
+        <v>-3.6624</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0414</v>
+        <v>-3.1425</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8713</v>
+        <v>-0.5199</v>
       </c>
       <c r="G23" t="n">
         <v>-0.1813</v>
@@ -2248,13 +2248,13 @@
         <v>0.586</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4105</v>
+        <v>-0.1603</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0522</v>
+        <v>-0.1533</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3583</v>
+        <v>-0.007</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>G. FERRARI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8116</v>
+        <v>-4.4068</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.4953</v>
+        <v>-1.4667</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3163</v>
+        <v>-2.9401</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.9095</v>
+        <v>-2.2679</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.6115</v>
+        <v>-0.1504</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7019</v>
+        <v>-2.1174</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.1403</v>
+        <v>-0.979</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.5736</v>
+        <v>0.3287</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4333</v>
+        <v>-1.3077</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.7692</v>
+        <v>-1.2889</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0379</v>
+        <v>-0.4792</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2687</v>
+        <v>-0.8097</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.3907</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9569</v>
+        <v>0.1383</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4015</v>
+        <v>-0.1203</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5554</v>
+        <v>0.2586</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5545</v>
+        <v>-1.4959</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5545</v>
+        <v>-2.1052</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>G. FERRARI</t>
+          <t>F. ALVAREZ BACO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.8995</v>
+        <v>-4.6883</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.7701</v>
+        <v>-4.6975</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.1294</v>
+        <v>0.0092</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.2679</v>
+        <v>-2.9095</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1504</v>
+        <v>-3.6115</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.1174</v>
+        <v>0.7019</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.979</v>
+        <v>-2.1403</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3287</v>
+        <v>-2.5736</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.3077</v>
+        <v>0.4333</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.2889</v>
+        <v>-0.7692</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4792</v>
+        <v>-1.0379</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.8097</v>
+        <v>0.2687</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.7814</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3544</v>
+        <v>-0.8336</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4237</v>
+        <v>-0.6038</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0693</v>
+        <v>-0.2299</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.4959</v>
+        <v>-0.5545</v>
       </c>
       <c r="W25" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.1052</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-31.682</v>
+        <v>-30.3336</v>
       </c>
       <c r="E26" t="n">
-        <v>-14.2638</v>
+        <v>-14.2639</v>
       </c>
       <c r="F26" t="n">
-        <v>-17.4182</v>
+        <v>-16.0699</v>
       </c>
       <c r="G26" t="n">
         <v>-18.5599</v>
@@ -2461,7 +2461,7 @@
         <v>-0.1307999999999994</v>
       </c>
       <c r="L26" t="n">
-        <v>4.7247</v>
+        <v>4.724700000000001</v>
       </c>
       <c r="M26" t="n">
         <v>-23.1538</v>
@@ -2473,7 +2473,7 @@
         <v>-14.846</v>
       </c>
       <c r="P26" t="n">
-        <v>-6.837</v>
+        <v>-6.836999999999999</v>
       </c>
       <c r="Q26" t="n">
         <v>-20.5109</v>
@@ -2482,13 +2482,13 @@
         <v>13.6739</v>
       </c>
       <c r="S26" t="n">
-        <v>-6.6721</v>
+        <v>-5.3239</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.6622</v>
+        <v>-4.6624</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.0098</v>
+        <v>-0.6617000000000002</v>
       </c>
       <c r="V26" t="n">
         <v>0.3866999999999996</v>
@@ -2497,7 +2497,7 @@
         <v>6.315399999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.928599999999999</v>
+        <v>-5.9286</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484368_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484368_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +653,78 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2874</v>
+        <v>5.3001</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8818</v>
+        <v>4.5793</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4056</v>
+        <v>0.7208</v>
       </c>
       <c r="G3" t="n">
-        <v>6.0838</v>
+        <v>5.4558</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1042</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>3.9797</v>
+        <v>4.7082</v>
       </c>
       <c r="J3" t="n">
-        <v>5.355</v>
+        <v>6.2893</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1051</v>
+        <v>1.3111</v>
       </c>
       <c r="L3" t="n">
-        <v>4.2499</v>
+        <v>4.9783</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7288</v>
+        <v>-0.8336</v>
       </c>
       <c r="N3" t="n">
-        <v>0.999</v>
+        <v>-0.5636</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2702</v>
+        <v>-0.27</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7814</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S3" t="n">
-        <v>0.985</v>
+        <v>0.1885</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4802</v>
+        <v>0.0015</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5047</v>
+        <v>0.187</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +736,72 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.3001</v>
+        <v>4.1525</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5793</v>
+        <v>1.7469</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7208</v>
+        <v>2.4056</v>
       </c>
       <c r="G4" t="n">
-        <v>5.4558</v>
+        <v>3.9489</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7475000000000001</v>
+        <v>1.1832</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7082</v>
+        <v>2.7657</v>
       </c>
       <c r="J4" t="n">
-        <v>6.2893</v>
+        <v>3.2201</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3111</v>
+        <v>0.1842</v>
       </c>
       <c r="L4" t="n">
-        <v>4.9783</v>
+        <v>3.0359</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8336</v>
+        <v>0.7288</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5636</v>
+        <v>0.999</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.27</v>
+        <v>-0.2702</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5627</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1885</v>
+        <v>0.985</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0015</v>
+        <v>0.4802</v>
       </c>
       <c r="U4" t="n">
-        <v>0.187</v>
+        <v>0.5047</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.8279</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,11 +1047,16 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6095</v>
+        <v>2.1349</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6365</v>
+        <v>2.1349</v>
       </c>
       <c r="F8" t="n">
-        <v>0.973</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6093</v>
+        <v>2.1349</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3395</v>
+        <v>0.921</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2698</v>
+        <v>1.214</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2569</v>
+        <v>2.1349</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3123</v>
+        <v>0.921</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9445</v>
+        <v>1.214</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6476</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9729</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6747</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3441</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3323</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0558</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2764</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2303</v>
+        <v>1.6095</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5726</v>
+        <v>0.6365</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6577</v>
+        <v>0.973</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5643</v>
+        <v>0.6093</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6861</v>
+        <v>0.3395</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1218</v>
+        <v>0.2698</v>
       </c>
       <c r="J9" t="n">
-        <v>0.305</v>
+        <v>2.2569</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0217</v>
+        <v>1.3123</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2833</v>
+        <v>0.9445</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2593</v>
+        <v>-1.6476</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6644</v>
+        <v>-0.9729</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4051</v>
+        <v>-0.6747</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9534</v>
+        <v>0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9534</v>
+        <v>2.3441</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2084</v>
+        <v>0.3323</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3417</v>
+        <v>0.0558</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5501</v>
+        <v>0.2764</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4959</v>
+        <v>0.2772</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1052</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>A. RUIZ CANAMERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1142</v>
+        <v>1.2303</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0044</v>
+        <v>0.5726</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1097</v>
+        <v>0.6577</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9301</v>
+        <v>0.5643</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8366</v>
+        <v>0.6861</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.7667</v>
+        <v>-0.1218</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1245</v>
+        <v>0.305</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1023</v>
+        <v>0.0217</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2268</v>
+        <v>0.2833</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1944</v>
+        <v>0.2593</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7342</v>
+        <v>0.6644</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5399</v>
+        <v>-0.4051</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7903</v>
+        <v>0.2084</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5744</v>
+        <v>-0.3417</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2159</v>
+        <v>0.5501</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2772</v>
+        <v>-1.4959</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5545</v>
+        <v>0.6093</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2772</v>
+        <v>-2.1052</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0118</v>
+        <v>1.1142</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3789</v>
+        <v>0.0044</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3906</v>
+        <v>1.1097</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3537</v>
+        <v>-0.9301</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8307</v>
+        <v>0.8366</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.1844</v>
+        <v>-1.7667</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4086</v>
+        <v>-1.1245</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3709</v>
+        <v>0.1023</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.7795</v>
+        <v>-1.2268</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0549</v>
+        <v>0.1944</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4597</v>
+        <v>0.7342</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4049</v>
+        <v>-0.5399</v>
       </c>
       <c r="P11" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1115</v>
+        <v>0.7903</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3385</v>
+        <v>0.5744</v>
       </c>
       <c r="U11" t="n">
-        <v>0.773</v>
+        <v>0.2159</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3321</v>
+        <v>0.2772</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3321</v>
+        <v>0.5545</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1105</v>
+        <v>0.0118</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4838</v>
+        <v>-2.3789</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5943000000000001</v>
+        <v>2.3906</v>
       </c>
       <c r="G12" t="n">
-        <v>0.126</v>
+        <v>-1.3537</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3796</v>
+        <v>0.8307</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2536</v>
+        <v>-2.1844</v>
       </c>
       <c r="J12" t="n">
-        <v>1.7687</v>
+        <v>-1.4086</v>
       </c>
       <c r="K12" t="n">
-        <v>2.2128</v>
+        <v>0.3709</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4441</v>
+        <v>-1.7795</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6427</v>
+        <v>0.0549</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8332000000000001</v>
+        <v>0.4597</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8095</v>
+        <v>-0.4049</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1488</v>
+        <v>1.5627</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1542</v>
+        <v>1.1115</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4266</v>
+        <v>0.3385</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7276</v>
+        <v>0.773</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6093</v>
+        <v>-0.3321</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2186</v>
+        <v>-0.3321</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,664 +1483,700 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>31.9845</v>
+        <v>-0.1105</v>
       </c>
       <c r="E13" t="n">
-        <v>17.7207</v>
+        <v>0.4838</v>
       </c>
       <c r="F13" t="n">
-        <v>14.2638</v>
+        <v>-0.5943000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>18.5598</v>
+        <v>0.126</v>
       </c>
       <c r="H13" t="n">
-        <v>8.438400000000001</v>
+        <v>1.3796</v>
       </c>
       <c r="I13" t="n">
-        <v>10.1213</v>
+        <v>-1.2536</v>
       </c>
       <c r="J13" t="n">
-        <v>23.1536</v>
+        <v>1.7687</v>
       </c>
       <c r="K13" t="n">
-        <v>8.307499999999999</v>
+        <v>2.2128</v>
       </c>
       <c r="L13" t="n">
-        <v>14.8461</v>
+        <v>-0.4441</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.5939</v>
+        <v>-1.6427</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1305999999999999</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.7247</v>
+        <v>-0.8095</v>
       </c>
       <c r="P13" t="n">
-        <v>6.836900000000001</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.6738</v>
+        <v>-2.9301</v>
       </c>
       <c r="R13" t="n">
-        <v>20.5109</v>
+        <v>2.1488</v>
       </c>
       <c r="S13" t="n">
-        <v>6.974699999999999</v>
+        <v>1.1542</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3124</v>
+        <v>0.4266</v>
       </c>
       <c r="U13" t="n">
-        <v>4.6621</v>
+        <v>0.7276</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3870000000000005</v>
+        <v>-0.6093</v>
       </c>
       <c r="W13" t="n">
-        <v>5.9285</v>
+        <v>1.2186</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.3154</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>TQ-CB PRAT</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4054</v>
+        <v>31.9845</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0357</v>
+        <v>17.7207</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6303</v>
+        <v>14.2638</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7012</v>
+        <v>18.5598</v>
       </c>
       <c r="H14" t="n">
-        <v>3.1049</v>
+        <v>8.4384</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.4037</v>
+        <v>10.1213</v>
       </c>
       <c r="J14" t="n">
-        <v>5.0235</v>
+        <v>23.1536</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7286</v>
+        <v>8.307599999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2949</v>
+        <v>14.8461</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.3223</v>
+        <v>-4.5939</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6237</v>
+        <v>0.1305999999999998</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.6986</v>
+        <v>-4.7247</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.5627</v>
+        <v>6.836900000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9301</v>
+        <v>-13.6738</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3674</v>
+        <v>20.5109</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0103</v>
+        <v>6.9747</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3349</v>
+        <v>2.3124</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3245</v>
+        <v>4.662100000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2772</v>
+        <v>-0.3870000000000005</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2772</v>
+        <v>5.9285</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
-      </c>
+        <v>-6.3154</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>J. BERTOMEU BALDÉ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.622</v>
+        <v>0.607</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2165</v>
+        <v>0.607</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8385</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2541</v>
+        <v>0.607</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4021</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.148</v>
+        <v>0.607</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7097</v>
+        <v>0.607</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6958</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0138</v>
+        <v>0.607</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9638</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.098</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1342</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0358</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.403</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3672</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.6075</v>
+        <v>0.4054</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1346</v>
+        <v>2.0357</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7421</v>
+        <v>-1.6303</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0404</v>
+        <v>1.7012</v>
       </c>
       <c r="H16" t="n">
-        <v>0.473</v>
+        <v>3.1049</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5134</v>
+        <v>-1.4037</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6962</v>
+        <v>5.0235</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1064</v>
+        <v>3.7286</v>
       </c>
       <c r="L16" t="n">
-        <v>2.5898</v>
+        <v>1.2949</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.7366</v>
+        <v>-3.3223</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6334</v>
+        <v>-0.6237</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.1032</v>
+        <v>-2.6986</v>
       </c>
       <c r="P16" t="n">
         <v>-1.5627</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.9069</v>
+        <v>-2.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3441</v>
+        <v>1.3674</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.223</v>
+        <v>-0.0103</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8734</v>
+        <v>-0.3349</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3496</v>
+        <v>0.3245</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. CANTALEJO DELGADO</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.9042</v>
+        <v>0.307</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.013</v>
+        <v>0.307</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8912</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.398</v>
+        <v>0.307</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4502</v>
+        <v>0.307</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.8482</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1047</v>
+        <v>0.307</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0642</v>
+        <v>0.307</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.5026</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.8887</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1616</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.141</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3026</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1176</v>
+        <v>-0.622</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4752</v>
+        <v>0.2165</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6424</v>
+        <v>-0.8385</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.7349</v>
+        <v>-0.2541</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4434</v>
+        <v>-0.4021</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.2915</v>
+        <v>0.148</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2033</v>
+        <v>0.7097</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6102</v>
+        <v>0.6958</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.0138</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.5316</v>
+        <v>-0.9638</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-1.098</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.6984</v>
+        <v>0.1342</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9334</v>
+        <v>-0.0358</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7324000000000001</v>
+        <v>-0.403</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.201</v>
+        <v>0.3672</v>
       </c>
       <c r="V18" t="n">
-        <v>2.7693</v>
+        <v>-0.3321</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4373</v>
+        <v>0.8865</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3321</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. TURNQUEST</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6184</v>
+        <v>-1.6075</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7328</v>
+        <v>0.1346</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8856</v>
+        <v>-1.7421</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-0.0404</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5866</v>
+        <v>0.473</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9572000000000001</v>
+        <v>-0.5134</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6194</v>
+        <v>3.6962</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.3073</v>
+        <v>1.1064</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6879</v>
+        <v>2.5898</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0101</v>
+        <v>-3.7366</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2793</v>
+        <v>-0.6334</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2692</v>
+        <v>-3.1032</v>
       </c>
       <c r="P19" t="n">
-        <v>0.586</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R19" t="n">
-        <v>0.586</v>
+        <v>2.3441</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4698</v>
+        <v>-1.223</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1134</v>
+        <v>-0.8734</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3564</v>
+        <v>-0.3496</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.1052</v>
+        <v>1.2186</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1052</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>H. CANTALEJO DELGADO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7987</v>
+        <v>-1.9042</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5312</v>
+        <v>-0.013</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2676</v>
+        <v>-1.8912</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.3536</v>
+        <v>-1.398</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3277</v>
+        <v>0.4502</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0259</v>
+        <v>-1.8482</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3103</v>
+        <v>1.1047</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.0387</v>
+        <v>1.0642</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7284</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0433</v>
+        <v>-2.5026</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2891</v>
+        <v>-0.614</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7542</v>
+        <v>-1.8887</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2498</v>
+        <v>0.1616</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8535</v>
+        <v>-0.141</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3963</v>
+        <v>0.3026</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6093</v>
+        <v>-0.2772</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1493</v>
+        <v>-2.4246</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8885</v>
+        <v>-0.7822</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2608</v>
+        <v>-1.6424</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.494</v>
+        <v>-5.0419</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8611</v>
+        <v>-1.7503</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6328</v>
+        <v>-3.2915</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1726</v>
+        <v>-1.5103</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.1627</v>
+        <v>-0.9171</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3354</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.6666</v>
+        <v>-3.5316</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6984</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.9682</v>
+        <v>-2.6984</v>
       </c>
       <c r="P21" t="n">
         <v>0.7814</v>
@@ -2092,413 +2188,688 @@
         <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.714</v>
+        <v>-0.9334</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3617</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3523</v>
+        <v>-0.201</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2772</v>
+        <v>2.7693</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>2.4373</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>E. TURNQUEST</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1638</v>
+        <v>-2.6184</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7033</v>
+        <v>-0.7328</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5394</v>
+        <v>-1.8856</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9979</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.658</v>
+        <v>-1.5866</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6601</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.7781</v>
+        <v>-0.6194</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.8995</v>
+        <v>-1.3073</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1214</v>
+        <v>0.6879</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2198</v>
+        <v>-0.0101</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7585</v>
+        <v>-0.2793</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5387</v>
+        <v>0.2692</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0062</v>
+        <v>-0.4698</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0283</v>
+        <v>-0.1134</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0221</v>
+        <v>-0.3564</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-2.1052</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-2.1052</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. BERTOMEU BALDÉ</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6624</v>
+        <v>-2.7987</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1425</v>
+        <v>-1.5312</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5199</v>
+        <v>-1.2676</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1813</v>
+        <v>-2.3536</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5743</v>
+        <v>-1.3277</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7556</v>
+        <v>-1.0259</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9177</v>
+        <v>-0.3103</v>
       </c>
       <c r="K23" t="n">
-        <v>1.5375</v>
+        <v>-1.0387</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6198</v>
+        <v>0.7284</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.099</v>
+        <v>-2.0433</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.2891</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1358</v>
+        <v>-1.7542</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.3208</v>
+        <v>0.1953</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1603</v>
+        <v>-1.2498</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1533</v>
+        <v>-0.8535</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.007</v>
+        <v>-0.3963</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. FERRARI</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4068</v>
+        <v>-3.1493</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4667</v>
+        <v>-0.8885</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.9401</v>
+        <v>-2.2608</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.2679</v>
+        <v>-3.494</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1504</v>
+        <v>-1.8611</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.1174</v>
+        <v>-1.6328</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.979</v>
+        <v>0.1726</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3287</v>
+        <v>-1.1627</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.3077</v>
+        <v>1.3354</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2889</v>
+        <v>-3.6666</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4792</v>
+        <v>-0.6984</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8097</v>
+        <v>-2.9682</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.7814</v>
+        <v>0.7814</v>
       </c>
       <c r="Q24" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1953</v>
+        <v>1.7581</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1383</v>
+        <v>-0.714</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1203</v>
+        <v>-0.3617</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2586</v>
+        <v>-0.3523</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.4959</v>
+        <v>0.2772</v>
       </c>
       <c r="W24" t="n">
-        <v>0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1052</v>
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.6883</v>
+        <v>-3.1638</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.6975</v>
+        <v>-3.7033</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0092</v>
+        <v>0.5394</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.9095</v>
+        <v>-1.9979</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.6115</v>
+        <v>-2.658</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7019</v>
+        <v>0.6601</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.1403</v>
+        <v>-1.7781</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.5736</v>
+        <v>-1.8995</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4333</v>
+        <v>0.1214</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.7692</v>
+        <v>-0.2198</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.0379</v>
+        <v>-0.7585</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2687</v>
+        <v>0.5387</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.3907</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q25" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8336</v>
+        <v>0.0062</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6038</v>
+        <v>0.0283</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2299</v>
+        <v>-0.0221</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. BERTOMEU BALDE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
+        <v>-4.2694</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-3.7495</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.5199</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.7883</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.5743</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.3626</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.5375</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-1.2268</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1.099</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.9631999999999999</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.1358</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-3.3208</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.1603</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.1533</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>G. FERRARI</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-4.4068</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-1.4667</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-2.9401</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-2.2679</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.1504</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-2.1174</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-0.979</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-1.3077</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-1.2889</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.4792</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.8097</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.1383</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.1203</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.2586</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-2.1052</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>F. ALVAREZ BACO</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-4.6883</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-4.6975</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-2.9095</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-3.6115</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.7019</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-2.1403</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-2.5736</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.4333</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-0.7692</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-1.0379</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.2687</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-0.8336</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-0.6038</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.2299</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484368_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
         <v>-30.3336</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E29" t="n">
         <v>-14.2639</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F29" t="n">
         <v>-16.0699</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G29" t="n">
         <v>-18.5599</v>
       </c>
-      <c r="H26" t="n">
-        <v>-8.4384</v>
-      </c>
-      <c r="I26" t="n">
+      <c r="H29" t="n">
+        <v>-8.4383</v>
+      </c>
+      <c r="I29" t="n">
         <v>-10.1213</v>
       </c>
-      <c r="J26" t="n">
-        <v>4.594</v>
-      </c>
-      <c r="K26" t="n">
-        <v>-0.1307999999999994</v>
-      </c>
-      <c r="L26" t="n">
-        <v>4.724700000000001</v>
-      </c>
-      <c r="M26" t="n">
+      <c r="J29" t="n">
+        <v>4.593999999999999</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-0.1306999999999996</v>
+      </c>
+      <c r="L29" t="n">
+        <v>4.724699999999999</v>
+      </c>
+      <c r="M29" t="n">
         <v>-23.1538</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N29" t="n">
         <v>-8.3079</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O29" t="n">
         <v>-14.846</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P29" t="n">
         <v>-6.836999999999999</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q29" t="n">
         <v>-20.5109</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R29" t="n">
         <v>13.6739</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S29" t="n">
         <v>-5.3239</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T29" t="n">
         <v>-4.6624</v>
       </c>
-      <c r="U26" t="n">
-        <v>-0.6617000000000002</v>
-      </c>
-      <c r="V26" t="n">
+      <c r="U29" t="n">
+        <v>-0.6617</v>
+      </c>
+      <c r="V29" t="n">
         <v>0.3866999999999996</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W29" t="n">
         <v>6.315399999999999</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X29" t="n">
         <v>-5.9286</v>
       </c>
+      <c r="Y29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
